--- a/jpcore-r4b/develop/StructureDefinition-jp-relatedperson.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-relatedperson.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-relatedperson.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-relatedperson.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="309">
   <si>
     <t>Property</t>
   </si>
@@ -259,14 +259,14 @@
 </t>
   </si>
   <si>
-    <t>A person that is related to a patient, but who is not a direct target of care</t>
-  </si>
-  <si>
-    <t>Information about a person that is involved in the care for a patient, but who is not the target of healthcare, nor has a formal responsibility in the care process.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>患者に関連しているが、ケアの直接的な標的ではない人 / A person that is related to a patient, but who is not a direct target of care</t>
+  </si>
+  <si>
+    <t>患者のケアに関与しているが、ヘルスケアの標的ではなく、ケアプロセスに正式な責任を負う人に関する情報。 / Information about a person that is involved in the care for a patient, but who is not the target of healthcare, nor has a formal responsibility in the care process.</t>
+  </si>
+  <si>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>role</t>
@@ -288,13 +288,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -307,26 +307,26 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
     <t>RelatedPerson.meta.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -346,13 +346,13 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -368,23 +368,27 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>RelatedPerson.meta.versionId</t>
   </si>
   <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+    <t>バージョン固有のidentifier (Baajon koyū no shikibetsu-shi) / Version specific identifier</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有のidentifier。この値は、リソースが作成、更新、または削除された場合に変更されます。 / The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。 / The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
   </si>
   <si>
     <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
   </si>
   <si>
     <t>RelatedPerson.meta.lastUpdated</t>
@@ -394,13 +398,13 @@
 </t>
   </si>
   <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
+    <t>リソースのバージョンが最後に変更されたとき / When the resource version last changed</t>
+  </si>
+  <si>
+    <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。 / When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>この値はリソースが初めて作成される場合を除いて常に設定されています。サーバー/リソースマネージャーがこの値を設定します。クライアントが提供する値は関係ありません。これはHTTP Last-Modifiedに相当し、[read](http://hl7.org/fhir/R4B/http.html#read)のインタラクションで同じ値を持つべきです。 / This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
   </si>
   <si>
     <t>Meta.lastUpdated</t>
@@ -413,13 +417,14 @@
 </t>
   </si>
   <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+    <t>リソースがどこから来たかを特定する / Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。 / A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。 / In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
 This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
   </si>
   <si>
@@ -433,13 +438,13 @@
 </t>
   </si>
   <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+    <t>このリソースが適合を主張するプロファイル / Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>このリソースが準拠すると主張する [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) リソースに関するプロファイルのリストです。URL は [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url) への参照です。 / A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>これらの主張が時間の経過に伴って検証または更新される方法と、それらを決定するサーバーや他の基盤に任されます。プロファイルURLのリストは1セットです。 / It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
     <t>Meta.profile</t>
@@ -452,13 +457,13 @@
 </t>
   </si>
   <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+    <t>このリソースに適用されたセキュリティラベル / Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>このリソースにはセキュリティラベルが適用されています。これらのタグにより、特定のリソースが全体的なセキュリティポリシーやインフラストラクチャに関連付けられます。 / Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>セキュリティラベルは変更せずにリソースのバージョンを更新可能です。セキュリティラベルのリストはセットであり、一意性はシステム/コードに基づき、バージョンと表示は無視されます。 / The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -473,13 +478,13 @@
     <t>RelatedPerson.meta.tag</t>
   </si>
   <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+    <t>このリソースに適用されたタグ / Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>このリソースに適用されるタグです。タグは、リソースをプロセスやワークフローに識別し、関連付けるために使用することが意図されており、アプリケーションはリソースの意味を解釈する際にタグを考慮する必要はありません。 / Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>リソースの表示バージョンを変更することなく、タグを更新できます。タグのリストは集合です。ユニーク性はシステム/コードに基づき、バージョンと表示は無視されます。 / The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
   </si>
   <si>
     <t>example</t>
@@ -494,13 +499,13 @@
     <t>RelatedPerson.implicitRules</t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -513,19 +518,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -545,13 +550,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -571,19 +576,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -593,23 +598,34 @@
     <t>RelatedPerson.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>RelatedPerson.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -622,13 +638,13 @@
 </t>
   </si>
   <si>
-    <t>A human identifier for this person</t>
-  </si>
-  <si>
-    <t>Identifier for a person within a particular scope.</t>
-  </si>
-  <si>
-    <t>People are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the patient. Examples are national person identifier and local identifier.</t>
+    <t>この人の人間のidentifier / A human identifier for this person</t>
+  </si>
+  <si>
+    <t>特定の範囲内の人のidentifier。 / Identifier for a person within a particular scope.</t>
+  </si>
+  <si>
+    <t>人々はさまざまなIDで知られています。一部の機関は、患者に関する他の組織と交換のためにいくつかのidentifierを維持しています。例は、国民のidentifierとローカルidentifierです。 / People are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the patient. Examples are national person identifier and local identifier.</t>
   </si>
   <si>
     <t>.id</t>
@@ -647,19 +663,19 @@
 </t>
   </si>
   <si>
-    <t>Whether this related person's record is in active use</t>
-  </si>
-  <si>
-    <t>Whether this related person record is in active use.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
-  </si>
-  <si>
-    <t>Need to be able to mark a related person record as not to be used, such as if it was created in error.</t>
-  </si>
-  <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+    <t>この関連者の記録が積極的に使用されているかどうか / Whether this related person's record is in active use</t>
+  </si>
+  <si>
+    <t>この関連者の記録が積極的に使用されているかどうか。 / Whether this related person record is in active use.</t>
+  </si>
+  <si>
+    <t>この要素は、リソースが誤って作成されたことをマークするために使用できるため、修飾子としてラベル付けされています。 / This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
+  </si>
+  <si>
+    <t>エラーで作成された場合など、使用されないように関連する人のレコードをマークできる必要があります。 / Need to be able to mark a related person record as not to be used, such as if it was created in error.</t>
+  </si>
+  <si>
+    <t>このリソースは、アクティブな要素の値が提供されていない場合、一般にアクティブであると想定されています / This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
     <t>.statusCode</t>
@@ -675,13 +691,13 @@
 </t>
   </si>
   <si>
-    <t>The patient this person is related to</t>
-  </si>
-  <si>
-    <t>The patient this person is related to.</t>
-  </si>
-  <si>
-    <t>We need to know which patient this RelatedPerson is related to.</t>
+    <t>この人が関係している患者 / The patient this person is related to</t>
+  </si>
+  <si>
+    <t>この人が関係している患者。 / The patient this person is related to.</t>
+  </si>
+  <si>
+    <t>この関連者がどの患者に関連しているかを知る必要があります。 / We need to know which patient this RelatedPerson is related to.</t>
   </si>
   <si>
     <t>scoper[classCode=PSN|ANM and determinerCode='INSTANCE']/playedRole[classCode='PAT']/id</t>
@@ -697,13 +713,13 @@
 </t>
   </si>
   <si>
-    <t>The nature of the relationship</t>
-  </si>
-  <si>
-    <t>The nature of the relationship between a patient and the related person.</t>
-  </si>
-  <si>
-    <t>We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
+    <t>関係の性質 / The nature of the relationship</t>
+  </si>
+  <si>
+    <t>患者と関連者との関係の性質。 / The nature of the relationship between a patient and the related person.</t>
+  </si>
+  <si>
+    <t>患者は、この人に起因する情報の解釈に影響を与えるため、患者との関係を知る必要があります。 / We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype|4.3.0</t>
@@ -725,13 +741,13 @@
 </t>
   </si>
   <si>
-    <t>A name associated with the person</t>
-  </si>
-  <si>
-    <t>A name associated with the person.</t>
-  </si>
-  <si>
-    <t>Related persons need to be identified by name, but it is uncommon to need details about multiple other names for that person.</t>
+    <t>人に関連付けられた名前 / A name associated with the person</t>
+  </si>
+  <si>
+    <t>人に関連付けられた名前。 / A name associated with the person.</t>
+  </si>
+  <si>
+    <t>関連者は名前で識別される必要がありますが、その人の他の複数の名前に関する詳細が必要であることは珍しいことです。 / Related persons need to be identified by name, but it is uncommon to need details about multiple other names for that person.</t>
   </si>
   <si>
     <t>name</t>
@@ -747,16 +763,16 @@
 </t>
   </si>
   <si>
-    <t>A contact detail for the person</t>
-  </si>
-  <si>
-    <t>A contact detail for the person, e.g. a telephone number or an email address.</t>
-  </si>
-  <si>
-    <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently, and also to help with identification.</t>
-  </si>
-  <si>
-    <t>People have (primary) ways to contact them in some way such as phone, email.</t>
+    <t>人の連絡先の詳細 / A contact detail for the person</t>
+  </si>
+  <si>
+    <t>人の連絡先の詳細、例えば電話番号またはメールアドレス。 / A contact detail for the person, e.g. a telephone number or an email address.</t>
+  </si>
+  <si>
+    <t>人には、さまざまな用途または適用される期間で連絡するための複数の方法があります。人に緊急に連絡するためのオプションが必要な場合があります。また、識別を支援する必要があります。 / Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently, and also to help with identification.</t>
+  </si>
+  <si>
+    <t>人々は、電話、電子メールなど、何らかの方法でそれらに連絡する（プライマリ）方法を持っています。 / People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
     <t>telecom</t>
@@ -768,19 +784,19 @@
     <t>RelatedPerson.gender</t>
   </si>
   <si>
-    <t>male | female | other | unknown</t>
-  </si>
-  <si>
-    <t>Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
-  </si>
-  <si>
-    <t>Needed for identification of the person, in combination with (at least) name and birth date.</t>
+    <t>男性|女性|その他|わからない / male | female | other | unknown</t>
+  </si>
+  <si>
+    <t>管理性別 - その人が管理と記録保持の目的で持っていると考えられている性別。 / Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
+  </si>
+  <si>
+    <t>（少なくとも）名前と生年月日と組み合わせて、その人の識別に必要です。 / Needed for identification of the person, in combination with (at least) name and birth date.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>The gender of a person used for administrative purposes.</t>
+    <t>管理目的で使用される人の性別。 / The gender of a person used for administrative purposes.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.3.0</t>
@@ -799,10 +815,10 @@
 </t>
   </si>
   <si>
-    <t>The date on which the related person was born</t>
-  </si>
-  <si>
-    <t>The date on which the related person was born.</t>
+    <t>関連者が生まれた日付 / The date on which the related person was born</t>
+  </si>
+  <si>
+    <t>関連者が生まれた日付。 / The date on which the related person was born.</t>
   </si>
   <si>
     <t>player.birthTime</t>
@@ -815,13 +831,13 @@
 </t>
   </si>
   <si>
-    <t>Address where the related person can be contacted or visited</t>
-  </si>
-  <si>
-    <t>Address where the related person can be contacted or visited.</t>
-  </si>
-  <si>
-    <t>Need to keep track where the related person can be contacted per postal mail or visited.</t>
+    <t>関連者に連絡または訪問できる場所アドレス / Address where the related person can be contacted or visited</t>
+  </si>
+  <si>
+    <t>関連者に連絡または訪問できる場所に住所します。 / Address where the related person can be contacted or visited.</t>
+  </si>
+  <si>
+    <t>郵便メールごとに関連する人に連絡するか、訪問できる場所を追跡する必要があります。 / Need to keep track where the related person can be contacted per postal mail or visited.</t>
   </si>
   <si>
     <t>addr</t>
@@ -837,13 +853,13 @@
 </t>
   </si>
   <si>
-    <t>Image of the person</t>
-  </si>
-  <si>
-    <t>Image of the person.</t>
-  </si>
-  <si>
-    <t>Many EHR systems have the capability to capture an image of persons. Fits with newer social media usage too.</t>
+    <t>人の画像 / Image of the person</t>
+  </si>
+  <si>
+    <t>人の画像。 / Image of the person.</t>
+  </si>
+  <si>
+    <t>多くのEHRシステムには、人のイメージをキャプチャする機能があります。新しいソーシャルメディアの使用にも適しています。 / Many EHR systems have the capability to capture an image of persons. Fits with newer social media usage too.</t>
   </si>
   <si>
     <t>player[classCode='PSN' and determinerCode='INSTANCE']/desc</t>
@@ -859,10 +875,10 @@
 </t>
   </si>
   <si>
-    <t>Period of time that this relationship is considered valid</t>
-  </si>
-  <si>
-    <t>The period of time during which this relationship is or was active. If there are no dates defined, then the interval is unknown.</t>
+    <t>この関係が有効と見なされる期間 / Period of time that this relationship is considered valid</t>
+  </si>
+  <si>
+    <t>この関係がアクティブであった期間。定義された日付がない場合、間隔は不明です。 / The period of time during which this relationship is or was active. If there are no dates defined, then the interval is unknown.</t>
   </si>
   <si>
     <t>.effectiveTime</t>
@@ -878,19 +894,19 @@
 </t>
   </si>
   <si>
-    <t>A language which may be used to communicate with about the patient's health</t>
-  </si>
-  <si>
-    <t>A language which may be used to communicate with about the patient's health.</t>
-  </si>
-  <si>
-    <t>If no language is specified, this *implies* that the default local language is spoken.  If you need to convey proficiency for multiple modes, then you need multiple RelatedPerson.Communication associations.   If the RelatedPerson does not speak the default local language, then the Interpreter Required Standard can be used to explicitly declare that an interpreter is required.</t>
-  </si>
-  <si>
-    <t>If a related person does not speak the local language, interpreters may be required, so languages spoken and proficiency is an important things to keep track of both for patient and other persons of interest.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>患者の健康についてコミュニケーションをとるために使用できる言語 / A language which may be used to communicate with about the patient's health</t>
+  </si>
+  <si>
+    <t>患者の健康について通信するために使用される言語。 / A language which may be used to communicate with about the patient's health.</t>
+  </si>
+  <si>
+    <t>言語が指定されていない場合、これは *デフォルトのローカル言語が話されていることを意味します。複数のモードに習熟度を伝える必要がある場合は、複数の関連者。コミュニケーション協会が必要です。関連者がデフォルトのローカル言語を話さない場合、インタープリターが必要とする標準を使用して、インタープリターが必要であることを明示的に宣言することができます。 / If no language is specified, this *implies* that the default local language is spoken.  If you need to convey proficiency for multiple modes, then you need multiple RelatedPerson.Communication associations.   If the RelatedPerson does not speak the default local language, then the Interpreter Required Standard can be used to explicitly declare that an interpreter is required.</t>
+  </si>
+  <si>
+    <t>関連者が地元の言語を話さない場合、通訳者が必要になる場合があるため、言語と習熟度は、患者や他の関心のある人の両方を追跡するための重要なことです。 / If a related person does not speak the local language, interpreters may be required, so languages spoken and proficiency is an important things to keep track of both for patient and other persons of interest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -904,7 +920,16 @@
 </t>
   </si>
   <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
     <t>RelatedPerson.communication.extension</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>RelatedPerson.communication.modifierExtension</t>
@@ -914,10 +939,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -927,16 +953,16 @@
     <t>RelatedPerson.communication.language</t>
   </si>
   <si>
-    <t>The language which can be used to communicate with the patient about his or her health</t>
-  </si>
-  <si>
-    <t>The ISO-639-1 alpha 2 code in lower case for the language, optionally followed by a hyphen and the ISO-3166-1 alpha 2 code for the region in upper case; e.g. "en" for English, or "en-US" for American English versus "en-EN" for England English.</t>
-  </si>
-  <si>
-    <t>The structure aa-BB with this exact casing is one the most widely used notations for locale. However not all systems actually code this but instead have it as free text. Hence CodeableConcept instead of code as the data type.</t>
-  </si>
-  <si>
-    <t>Most systems in multilingual countries will want to convey language. Not all systems actually need the regional dialect.</t>
+    <t>患者と自分の健康についてコミュニケーションをとるために使用できる言語 / The language which can be used to communicate with the patient about his or her health</t>
+  </si>
+  <si>
+    <t>ISO-639-1アルファ2コードは言語の小文字で、オプションでハイフンとISO-3166-1アルファ2コードが上品な領域のコードを続けます。例えば英語の「en」、またはイングランド英語のアメリカ英語と「en-en」の「en-us」。 / The ISO-639-1 alpha 2 code in lower case for the language, optionally followed by a hyphen and the ISO-3166-1 alpha 2 code for the region in upper case; e.g. "en" for English, or "en-US" for American English versus "en-EN" for England English.</t>
+  </si>
+  <si>
+    <t>この正確なケーシングを備えた構造AA-BBは、ロケールで最も広く使用されている表記法の1つです。ただし、すべてのシステムが実際にこれをコーディングするわけではありませんが、代わりに無料のテキストとして持っています。したがって、データ型としてコードの代わりにCodeableconcept。 / The structure aa-BB with this exact casing is one the most widely used notations for locale. However not all systems actually code this but instead have it as free text. Hence CodeableConcept instead of code as the data type.</t>
+  </si>
+  <si>
+    <t>多言語国のほとんどのシステムは、言語を伝えたいと思うでしょう。すべてのシステムが実際に地域の方言を必要とするわけではありません。 / Most systems in multilingual countries will want to convey language. Not all systems actually need the regional dialect.</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/languageCommunication/code</t>
@@ -945,16 +971,16 @@
     <t>RelatedPerson.communication.preferred</t>
   </si>
   <si>
-    <t>Language preference indicator</t>
-  </si>
-  <si>
-    <t>Indicates whether or not the patient prefers this language (over other languages he masters up a certain level).</t>
-  </si>
-  <si>
-    <t>This language is specifically identified for communicating healthcare information.</t>
-  </si>
-  <si>
-    <t>People that master multiple languages up to certain level may prefer one or more, i.e. feel more confident in communicating in a particular language making other languages sort of a fall back method.</t>
+    <t>言語選好インジケーター / Language preference indicator</t>
+  </si>
+  <si>
+    <t>患者がこの言語を好むかどうかを示します（他の言語よりも、彼は一定のレベルをマスターします）。 / Indicates whether or not the patient prefers this language (over other languages he masters up a certain level).</t>
+  </si>
+  <si>
+    <t>この言語は、ヘルスケア情報の伝達のために特別に特定されています。 / This language is specifically identified for communicating healthcare information.</t>
+  </si>
+  <si>
+    <t>一定レベルまで複数の言語を習得する人は、1つ以上を好むかもしれません。つまり、他の言語をフォールバックの方法にする特定の言語で通信することに自信を持っていると感じます。 / People that master multiple languages up to certain level may prefer one or more, i.e. feel more confident in communicating in a particular language making other languages sort of a fall back method.</t>
   </si>
   <si>
     <t>preferenceInd</t>
@@ -1301,7 +1327,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="58.23828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="72.97265625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="51.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -2084,7 +2110,7 @@
         <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>76</v>
@@ -2098,10 +2124,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2124,16 +2150,16 @@
         <v>87</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2183,7 +2209,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2195,7 +2221,7 @@
         <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>76</v>
@@ -2209,10 +2235,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2235,16 +2261,16 @@
         <v>87</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2294,7 +2320,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2306,7 +2332,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -2320,10 +2346,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2346,16 +2372,16 @@
         <v>87</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2405,7 +2431,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2417,7 +2443,7 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2431,10 +2457,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2457,16 +2483,16 @@
         <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2492,11 +2518,11 @@
         <v>76</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y11" s="2"/>
       <c r="Z11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>76</v>
@@ -2514,7 +2540,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2526,7 +2552,7 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>76</v>
@@ -2540,10 +2566,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2566,16 +2592,16 @@
         <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2601,11 +2627,11 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>76</v>
@@ -2623,7 +2649,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2635,7 +2661,7 @@
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>76</v>
@@ -2649,10 +2675,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2675,16 +2701,16 @@
         <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2734,7 +2760,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2760,10 +2786,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2786,16 +2812,16 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2821,13 +2847,13 @@
         <v>76</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>76</v>
@@ -2845,7 +2871,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2871,14 +2897,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2897,16 +2923,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2956,7 +2982,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2971,7 +2997,7 @@
         <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>76</v>
@@ -2982,14 +3008,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3008,16 +3034,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3067,7 +3093,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3079,10 +3105,10 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3093,10 +3119,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3122,13 +3148,13 @@
         <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>107</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>109</v>
+        <v>188</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3178,7 +3204,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3190,10 +3216,10 @@
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3204,10 +3230,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3233,16 +3259,16 @@
         <v>106</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>109</v>
-      </c>
       <c r="O18" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -3291,7 +3317,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3303,10 +3329,10 @@
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -3317,10 +3343,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3343,17 +3369,17 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3402,7 +3428,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3417,21 +3443,21 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3454,70 +3480,70 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="P20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="R20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="P20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="R20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3532,10 +3558,10 @@
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>76</v>
@@ -3543,10 +3569,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3569,17 +3595,17 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3628,7 +3654,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>86</v>
@@ -3643,21 +3669,21 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3680,17 +3706,17 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -3715,13 +3741,13 @@
         <v>76</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>76</v>
@@ -3739,7 +3765,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3754,21 +3780,21 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3791,17 +3817,17 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -3850,7 +3876,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3865,21 +3891,21 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3902,19 +3928,19 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -3963,7 +3989,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3978,21 +4004,21 @@
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4015,17 +4041,17 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4050,31 +4076,31 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4089,21 +4115,21 @@
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4126,13 +4152,13 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4183,7 +4209,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4198,7 +4224,7 @@
         <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
@@ -4209,10 +4235,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4235,17 +4261,17 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4294,7 +4320,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4309,21 +4335,21 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4346,17 +4372,17 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4405,7 +4431,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4420,21 +4446,21 @@
         <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4457,13 +4483,13 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4514,7 +4540,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4529,10 +4555,10 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>76</v>
@@ -4540,10 +4566,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4566,19 +4592,19 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -4627,7 +4653,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4639,10 +4665,10 @@
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
@@ -4653,10 +4679,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4679,13 +4705,13 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>100</v>
+        <v>288</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>101</v>
+        <v>289</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4762,10 +4788,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4791,13 +4817,13 @@
         <v>106</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>107</v>
+        <v>186</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>108</v>
+        <v>291</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>109</v>
+        <v>188</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4859,7 +4885,7 @@
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>103</v>
@@ -4873,14 +4899,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4902,16 +4928,16 @@
         <v>106</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>109</v>
+        <v>188</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -4960,7 +4986,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -4972,10 +4998,10 @@
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -4986,10 +5012,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5012,19 +5038,19 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -5049,13 +5075,13 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>76</v>
@@ -5073,7 +5099,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>86</v>
@@ -5088,7 +5114,7 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5099,10 +5125,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5125,19 +5151,19 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5186,7 +5212,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5201,7 +5227,7 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
